--- a/uizin-eventos/public/templates/Tournament_OS_選手入力テンプレート.xlsx
+++ b/uizin-eventos/public/templates/Tournament_OS_選手入力テンプレート.xlsx
@@ -804,6 +804,7 @@
     <x:col min="8" max="8" width="28" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="34" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="38" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="42" customHeight="1">
@@ -836,6 +837,9 @@
       </x:c>
       <x:c r="J1" s="53" t="str">
         <x:v>入場曲URL（Apple Music推奨）</x:v>
+      </x:c>
+      <x:c r="K1" s="53" t="str">
+        <x:v>クラス</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
@@ -849,6 +853,7 @@
       <x:c r="H2" s="55"/>
       <x:c r="I2" s="55"/>
       <x:c r="J2" s="57"/>
+      <x:c r="K2" s="55"/>
     </x:row>
     <x:row r="3" ht="30" customHeight="1">
       <x:c r="A3" s="54"/>
@@ -861,6 +866,7 @@
       <x:c r="H3" s="55"/>
       <x:c r="I3" s="55"/>
       <x:c r="J3" s="57"/>
+      <x:c r="K3" s="55"/>
     </x:row>
     <x:row r="4" ht="30" customHeight="1">
       <x:c r="A4" s="54"/>
@@ -873,6 +879,7 @@
       <x:c r="H4" s="55"/>
       <x:c r="I4" s="55"/>
       <x:c r="J4" s="57"/>
+      <x:c r="K4" s="55"/>
     </x:row>
     <x:row r="5" ht="30" customHeight="1">
       <x:c r="A5" s="54"/>
@@ -885,6 +892,7 @@
       <x:c r="H5" s="55"/>
       <x:c r="I5" s="55"/>
       <x:c r="J5" s="57"/>
+      <x:c r="K5" s="55"/>
     </x:row>
     <x:row r="6" ht="30" customHeight="1">
       <x:c r="A6" s="54"/>
@@ -897,6 +905,7 @@
       <x:c r="H6" s="55"/>
       <x:c r="I6" s="55"/>
       <x:c r="J6" s="57"/>
+      <x:c r="K6" s="55"/>
     </x:row>
     <x:row r="7" ht="30" customHeight="1">
       <x:c r="A7" s="54"/>
@@ -909,6 +918,7 @@
       <x:c r="H7" s="55"/>
       <x:c r="I7" s="55"/>
       <x:c r="J7" s="57"/>
+      <x:c r="K7" s="55"/>
     </x:row>
     <x:row r="8" ht="30" customHeight="1">
       <x:c r="A8" s="54"/>
@@ -921,6 +931,7 @@
       <x:c r="H8" s="55"/>
       <x:c r="I8" s="55"/>
       <x:c r="J8" s="57"/>
+      <x:c r="K8" s="55"/>
     </x:row>
     <x:row r="9" ht="30" customHeight="1">
       <x:c r="A9" s="54"/>
@@ -933,6 +944,7 @@
       <x:c r="H9" s="55"/>
       <x:c r="I9" s="55"/>
       <x:c r="J9" s="57"/>
+      <x:c r="K9" s="55"/>
     </x:row>
     <x:row r="10" ht="30" customHeight="1">
       <x:c r="A10" s="54"/>
@@ -945,6 +957,7 @@
       <x:c r="H10" s="55"/>
       <x:c r="I10" s="55"/>
       <x:c r="J10" s="57"/>
+      <x:c r="K10" s="55"/>
     </x:row>
     <x:row r="11" ht="30" customHeight="1">
       <x:c r="A11" s="54"/>
@@ -957,6 +970,7 @@
       <x:c r="H11" s="55"/>
       <x:c r="I11" s="55"/>
       <x:c r="J11" s="57"/>
+      <x:c r="K11" s="55"/>
     </x:row>
     <x:row r="12" ht="30" customHeight="1">
       <x:c r="A12" s="54"/>
@@ -969,6 +983,7 @@
       <x:c r="H12" s="55"/>
       <x:c r="I12" s="55"/>
       <x:c r="J12" s="57"/>
+      <x:c r="K12" s="55"/>
     </x:row>
     <x:row r="13" ht="30" customHeight="1">
       <x:c r="A13" s="54"/>
@@ -981,6 +996,7 @@
       <x:c r="H13" s="55"/>
       <x:c r="I13" s="55"/>
       <x:c r="J13" s="57"/>
+      <x:c r="K13" s="55"/>
     </x:row>
     <x:row r="14" ht="30" customHeight="1">
       <x:c r="A14" s="54"/>
@@ -993,6 +1009,7 @@
       <x:c r="H14" s="55"/>
       <x:c r="I14" s="55"/>
       <x:c r="J14" s="57"/>
+      <x:c r="K14" s="55"/>
     </x:row>
     <x:row r="15" ht="30" customHeight="1">
       <x:c r="A15" s="54"/>
@@ -1005,6 +1022,7 @@
       <x:c r="H15" s="55"/>
       <x:c r="I15" s="55"/>
       <x:c r="J15" s="57"/>
+      <x:c r="K15" s="55"/>
     </x:row>
     <x:row r="16" ht="30" customHeight="1">
       <x:c r="A16" s="54"/>
@@ -1017,6 +1035,7 @@
       <x:c r="H16" s="55"/>
       <x:c r="I16" s="55"/>
       <x:c r="J16" s="57"/>
+      <x:c r="K16" s="55"/>
     </x:row>
     <x:row r="17" ht="30" customHeight="1">
       <x:c r="A17" s="54"/>
@@ -1029,6 +1048,7 @@
       <x:c r="H17" s="55"/>
       <x:c r="I17" s="55"/>
       <x:c r="J17" s="57"/>
+      <x:c r="K17" s="55"/>
     </x:row>
     <x:row r="18" ht="30" customHeight="1">
       <x:c r="A18" s="54"/>
@@ -1041,6 +1061,7 @@
       <x:c r="H18" s="55"/>
       <x:c r="I18" s="55"/>
       <x:c r="J18" s="57"/>
+      <x:c r="K18" s="55"/>
     </x:row>
     <x:row r="19" ht="30" customHeight="1">
       <x:c r="A19" s="54"/>
@@ -1053,6 +1074,7 @@
       <x:c r="H19" s="55"/>
       <x:c r="I19" s="55"/>
       <x:c r="J19" s="57"/>
+      <x:c r="K19" s="55"/>
     </x:row>
     <x:row r="20" ht="30" customHeight="1">
       <x:c r="A20" s="54"/>
@@ -1065,6 +1087,7 @@
       <x:c r="H20" s="55"/>
       <x:c r="I20" s="55"/>
       <x:c r="J20" s="57"/>
+      <x:c r="K20" s="55"/>
     </x:row>
     <x:row r="21" ht="30" customHeight="1">
       <x:c r="A21" s="54"/>
@@ -1077,6 +1100,7 @@
       <x:c r="H21" s="55"/>
       <x:c r="I21" s="55"/>
       <x:c r="J21" s="57"/>
+      <x:c r="K21" s="55"/>
     </x:row>
     <x:row r="22" ht="30" customHeight="1">
       <x:c r="A22" s="54"/>
@@ -1089,6 +1113,7 @@
       <x:c r="H22" s="55"/>
       <x:c r="I22" s="55"/>
       <x:c r="J22" s="57"/>
+      <x:c r="K22" s="55"/>
     </x:row>
     <x:row r="23" ht="30" customHeight="1">
       <x:c r="A23" s="54"/>
@@ -1101,6 +1126,7 @@
       <x:c r="H23" s="55"/>
       <x:c r="I23" s="55"/>
       <x:c r="J23" s="57"/>
+      <x:c r="K23" s="55"/>
     </x:row>
     <x:row r="24" ht="30" customHeight="1">
       <x:c r="A24" s="54"/>
@@ -1113,6 +1139,7 @@
       <x:c r="H24" s="55"/>
       <x:c r="I24" s="55"/>
       <x:c r="J24" s="57"/>
+      <x:c r="K24" s="55"/>
     </x:row>
     <x:row r="25" ht="30" customHeight="1">
       <x:c r="A25" s="54"/>
@@ -1125,6 +1152,7 @@
       <x:c r="H25" s="55"/>
       <x:c r="I25" s="55"/>
       <x:c r="J25" s="57"/>
+      <x:c r="K25" s="55"/>
     </x:row>
     <x:row r="26" ht="30" customHeight="1">
       <x:c r="A26" s="54"/>
@@ -1137,6 +1165,7 @@
       <x:c r="H26" s="55"/>
       <x:c r="I26" s="55"/>
       <x:c r="J26" s="57"/>
+      <x:c r="K26" s="55"/>
     </x:row>
     <x:row r="27" ht="30" customHeight="1">
       <x:c r="A27" s="54"/>
@@ -1149,6 +1178,7 @@
       <x:c r="H27" s="55"/>
       <x:c r="I27" s="55"/>
       <x:c r="J27" s="57"/>
+      <x:c r="K27" s="55"/>
     </x:row>
     <x:row r="28" ht="30" customHeight="1">
       <x:c r="A28" s="54"/>
@@ -1161,6 +1191,7 @@
       <x:c r="H28" s="55"/>
       <x:c r="I28" s="55"/>
       <x:c r="J28" s="57"/>
+      <x:c r="K28" s="55"/>
     </x:row>
     <x:row r="29" ht="30" customHeight="1">
       <x:c r="A29" s="54"/>
@@ -1173,6 +1204,7 @@
       <x:c r="H29" s="55"/>
       <x:c r="I29" s="55"/>
       <x:c r="J29" s="57"/>
+      <x:c r="K29" s="55"/>
     </x:row>
     <x:row r="30" ht="30" customHeight="1">
       <x:c r="A30" s="54"/>
@@ -1185,6 +1217,7 @@
       <x:c r="H30" s="55"/>
       <x:c r="I30" s="55"/>
       <x:c r="J30" s="57"/>
+      <x:c r="K30" s="55"/>
     </x:row>
     <x:row r="31" ht="30" customHeight="1">
       <x:c r="A31" s="54"/>
@@ -1197,6 +1230,7 @@
       <x:c r="H31" s="55"/>
       <x:c r="I31" s="55"/>
       <x:c r="J31" s="57"/>
+      <x:c r="K31" s="55"/>
     </x:row>
     <x:row r="32" ht="30" customHeight="1">
       <x:c r="A32" s="54"/>
@@ -1209,6 +1243,7 @@
       <x:c r="H32" s="55"/>
       <x:c r="I32" s="55"/>
       <x:c r="J32" s="57"/>
+      <x:c r="K32" s="55"/>
     </x:row>
     <x:row r="33" ht="30" customHeight="1">
       <x:c r="A33" s="54"/>
@@ -1221,6 +1256,7 @@
       <x:c r="H33" s="55"/>
       <x:c r="I33" s="55"/>
       <x:c r="J33" s="57"/>
+      <x:c r="K33" s="55"/>
     </x:row>
     <x:row r="34" ht="30" customHeight="1">
       <x:c r="A34" s="54"/>
@@ -1233,6 +1269,7 @@
       <x:c r="H34" s="55"/>
       <x:c r="I34" s="55"/>
       <x:c r="J34" s="57"/>
+      <x:c r="K34" s="55"/>
     </x:row>
     <x:row r="35" ht="30" customHeight="1">
       <x:c r="A35" s="54"/>
@@ -1245,6 +1282,7 @@
       <x:c r="H35" s="55"/>
       <x:c r="I35" s="55"/>
       <x:c r="J35" s="57"/>
+      <x:c r="K35" s="55"/>
     </x:row>
     <x:row r="36" ht="30" customHeight="1">
       <x:c r="A36" s="54"/>
@@ -1257,6 +1295,7 @@
       <x:c r="H36" s="55"/>
       <x:c r="I36" s="55"/>
       <x:c r="J36" s="57"/>
+      <x:c r="K36" s="55"/>
     </x:row>
     <x:row r="37" ht="30" customHeight="1">
       <x:c r="A37" s="54"/>
@@ -1269,6 +1308,7 @@
       <x:c r="H37" s="55"/>
       <x:c r="I37" s="55"/>
       <x:c r="J37" s="57"/>
+      <x:c r="K37" s="55"/>
     </x:row>
     <x:row r="38" ht="30" customHeight="1">
       <x:c r="A38" s="54"/>
@@ -1281,6 +1321,7 @@
       <x:c r="H38" s="55"/>
       <x:c r="I38" s="55"/>
       <x:c r="J38" s="57"/>
+      <x:c r="K38" s="55"/>
     </x:row>
     <x:row r="39" ht="30" customHeight="1">
       <x:c r="A39" s="54"/>
@@ -1293,6 +1334,7 @@
       <x:c r="H39" s="55"/>
       <x:c r="I39" s="55"/>
       <x:c r="J39" s="57"/>
+      <x:c r="K39" s="55"/>
     </x:row>
     <x:row r="40" ht="30" customHeight="1">
       <x:c r="A40" s="54"/>
@@ -1305,6 +1347,7 @@
       <x:c r="H40" s="55"/>
       <x:c r="I40" s="55"/>
       <x:c r="J40" s="57"/>
+      <x:c r="K40" s="55"/>
     </x:row>
     <x:row r="41" ht="30" customHeight="1">
       <x:c r="A41" s="54"/>
@@ -1317,6 +1360,7 @@
       <x:c r="H41" s="55"/>
       <x:c r="I41" s="55"/>
       <x:c r="J41" s="57"/>
+      <x:c r="K41" s="55"/>
     </x:row>
     <x:row r="42" ht="30" customHeight="1">
       <x:c r="A42" s="54"/>
@@ -1329,6 +1373,7 @@
       <x:c r="H42" s="55"/>
       <x:c r="I42" s="55"/>
       <x:c r="J42" s="57"/>
+      <x:c r="K42" s="55"/>
     </x:row>
     <x:row r="43" ht="30" customHeight="1">
       <x:c r="A43" s="54"/>
@@ -1341,6 +1386,7 @@
       <x:c r="H43" s="55"/>
       <x:c r="I43" s="55"/>
       <x:c r="J43" s="57"/>
+      <x:c r="K43" s="55"/>
     </x:row>
     <x:row r="44" ht="30" customHeight="1">
       <x:c r="A44" s="54"/>
@@ -1353,6 +1399,7 @@
       <x:c r="H44" s="55"/>
       <x:c r="I44" s="55"/>
       <x:c r="J44" s="57"/>
+      <x:c r="K44" s="55"/>
     </x:row>
     <x:row r="45" ht="30" customHeight="1">
       <x:c r="A45" s="54"/>
@@ -1365,6 +1412,7 @@
       <x:c r="H45" s="55"/>
       <x:c r="I45" s="55"/>
       <x:c r="J45" s="57"/>
+      <x:c r="K45" s="55"/>
     </x:row>
     <x:row r="46" ht="30" customHeight="1">
       <x:c r="A46" s="54"/>
@@ -1377,6 +1425,7 @@
       <x:c r="H46" s="55"/>
       <x:c r="I46" s="55"/>
       <x:c r="J46" s="57"/>
+      <x:c r="K46" s="55"/>
     </x:row>
     <x:row r="47" ht="30" customHeight="1">
       <x:c r="A47" s="54"/>
@@ -1389,6 +1438,7 @@
       <x:c r="H47" s="55"/>
       <x:c r="I47" s="55"/>
       <x:c r="J47" s="57"/>
+      <x:c r="K47" s="55"/>
     </x:row>
     <x:row r="48" ht="30" customHeight="1">
       <x:c r="A48" s="54"/>
@@ -1401,6 +1451,7 @@
       <x:c r="H48" s="55"/>
       <x:c r="I48" s="55"/>
       <x:c r="J48" s="57"/>
+      <x:c r="K48" s="55"/>
     </x:row>
     <x:row r="49" ht="30" customHeight="1">
       <x:c r="A49" s="54"/>
@@ -1413,6 +1464,7 @@
       <x:c r="H49" s="55"/>
       <x:c r="I49" s="55"/>
       <x:c r="J49" s="57"/>
+      <x:c r="K49" s="55"/>
     </x:row>
     <x:row r="50" ht="30" customHeight="1">
       <x:c r="A50" s="54"/>
@@ -1425,6 +1477,7 @@
       <x:c r="H50" s="55"/>
       <x:c r="I50" s="55"/>
       <x:c r="J50" s="57"/>
+      <x:c r="K50" s="55"/>
     </x:row>
     <x:row r="51" ht="30" customHeight="1">
       <x:c r="A51" s="54"/>
@@ -1437,6 +1490,7 @@
       <x:c r="H51" s="55"/>
       <x:c r="I51" s="55"/>
       <x:c r="J51" s="57"/>
+      <x:c r="K51" s="55"/>
     </x:row>
     <x:row r="52" ht="30" customHeight="1">
       <x:c r="A52" s="54"/>
@@ -1449,6 +1503,7 @@
       <x:c r="H52" s="55"/>
       <x:c r="I52" s="55"/>
       <x:c r="J52" s="57"/>
+      <x:c r="K52" s="55"/>
     </x:row>
     <x:row r="53" ht="30" customHeight="1">
       <x:c r="A53" s="54"/>
@@ -1461,6 +1516,7 @@
       <x:c r="H53" s="55"/>
       <x:c r="I53" s="55"/>
       <x:c r="J53" s="57"/>
+      <x:c r="K53" s="55"/>
     </x:row>
     <x:row r="54" ht="30" customHeight="1">
       <x:c r="A54" s="54"/>
@@ -1473,6 +1529,7 @@
       <x:c r="H54" s="55"/>
       <x:c r="I54" s="55"/>
       <x:c r="J54" s="57"/>
+      <x:c r="K54" s="55"/>
     </x:row>
     <x:row r="55" ht="30" customHeight="1">
       <x:c r="A55" s="54"/>
@@ -1485,6 +1542,7 @@
       <x:c r="H55" s="55"/>
       <x:c r="I55" s="55"/>
       <x:c r="J55" s="57"/>
+      <x:c r="K55" s="55"/>
     </x:row>
     <x:row r="56" ht="30" customHeight="1">
       <x:c r="A56" s="54"/>
@@ -1497,6 +1555,7 @@
       <x:c r="H56" s="55"/>
       <x:c r="I56" s="55"/>
       <x:c r="J56" s="57"/>
+      <x:c r="K56" s="55"/>
     </x:row>
     <x:row r="57" ht="30" customHeight="1">
       <x:c r="A57" s="54"/>
@@ -1509,6 +1568,7 @@
       <x:c r="H57" s="55"/>
       <x:c r="I57" s="55"/>
       <x:c r="J57" s="57"/>
+      <x:c r="K57" s="55"/>
     </x:row>
     <x:row r="58" ht="30" customHeight="1">
       <x:c r="A58" s="54"/>
@@ -1521,6 +1581,7 @@
       <x:c r="H58" s="55"/>
       <x:c r="I58" s="55"/>
       <x:c r="J58" s="57"/>
+      <x:c r="K58" s="55"/>
     </x:row>
     <x:row r="59" ht="30" customHeight="1">
       <x:c r="A59" s="54"/>
@@ -1533,6 +1594,7 @@
       <x:c r="H59" s="55"/>
       <x:c r="I59" s="55"/>
       <x:c r="J59" s="57"/>
+      <x:c r="K59" s="55"/>
     </x:row>
     <x:row r="60" ht="30" customHeight="1">
       <x:c r="A60" s="54"/>
@@ -1545,6 +1607,7 @@
       <x:c r="H60" s="55"/>
       <x:c r="I60" s="55"/>
       <x:c r="J60" s="57"/>
+      <x:c r="K60" s="55"/>
     </x:row>
     <x:row r="61" ht="30" customHeight="1">
       <x:c r="A61" s="54"/>
@@ -1557,6 +1620,7 @@
       <x:c r="H61" s="55"/>
       <x:c r="I61" s="55"/>
       <x:c r="J61" s="57"/>
+      <x:c r="K61" s="55"/>
     </x:row>
     <x:row r="62" ht="30" customHeight="1">
       <x:c r="A62" s="54"/>
@@ -1569,6 +1633,7 @@
       <x:c r="H62" s="55"/>
       <x:c r="I62" s="55"/>
       <x:c r="J62" s="57"/>
+      <x:c r="K62" s="55"/>
     </x:row>
     <x:row r="63" ht="30" customHeight="1">
       <x:c r="A63" s="54"/>
@@ -1581,6 +1646,7 @@
       <x:c r="H63" s="55"/>
       <x:c r="I63" s="55"/>
       <x:c r="J63" s="57"/>
+      <x:c r="K63" s="55"/>
     </x:row>
     <x:row r="64" ht="30" customHeight="1">
       <x:c r="A64" s="54"/>
@@ -1593,6 +1659,7 @@
       <x:c r="H64" s="55"/>
       <x:c r="I64" s="55"/>
       <x:c r="J64" s="57"/>
+      <x:c r="K64" s="55"/>
     </x:row>
     <x:row r="65" ht="30" customHeight="1">
       <x:c r="A65" s="54"/>
@@ -1605,6 +1672,7 @@
       <x:c r="H65" s="55"/>
       <x:c r="I65" s="55"/>
       <x:c r="J65" s="57"/>
+      <x:c r="K65" s="55"/>
     </x:row>
     <x:row r="66" ht="30" customHeight="1">
       <x:c r="A66" s="54"/>
@@ -1617,6 +1685,7 @@
       <x:c r="H66" s="55"/>
       <x:c r="I66" s="55"/>
       <x:c r="J66" s="57"/>
+      <x:c r="K66" s="55"/>
     </x:row>
     <x:row r="67" ht="30" customHeight="1">
       <x:c r="A67" s="54"/>
@@ -1629,6 +1698,7 @@
       <x:c r="H67" s="55"/>
       <x:c r="I67" s="55"/>
       <x:c r="J67" s="57"/>
+      <x:c r="K67" s="55"/>
     </x:row>
     <x:row r="68" ht="30" customHeight="1">
       <x:c r="A68" s="54"/>
@@ -1641,6 +1711,7 @@
       <x:c r="H68" s="55"/>
       <x:c r="I68" s="55"/>
       <x:c r="J68" s="57"/>
+      <x:c r="K68" s="55"/>
     </x:row>
     <x:row r="69" ht="30" customHeight="1">
       <x:c r="A69" s="54"/>
@@ -1653,6 +1724,7 @@
       <x:c r="H69" s="55"/>
       <x:c r="I69" s="55"/>
       <x:c r="J69" s="57"/>
+      <x:c r="K69" s="55"/>
     </x:row>
     <x:row r="70" ht="30" customHeight="1">
       <x:c r="A70" s="54"/>
@@ -1665,6 +1737,7 @@
       <x:c r="H70" s="55"/>
       <x:c r="I70" s="55"/>
       <x:c r="J70" s="57"/>
+      <x:c r="K70" s="55"/>
     </x:row>
     <x:row r="71" ht="30" customHeight="1">
       <x:c r="A71" s="54"/>
@@ -1677,6 +1750,7 @@
       <x:c r="H71" s="55"/>
       <x:c r="I71" s="55"/>
       <x:c r="J71" s="57"/>
+      <x:c r="K71" s="55"/>
     </x:row>
     <x:row r="72" ht="30" customHeight="1">
       <x:c r="A72" s="54"/>
@@ -1689,6 +1763,7 @@
       <x:c r="H72" s="55"/>
       <x:c r="I72" s="55"/>
       <x:c r="J72" s="57"/>
+      <x:c r="K72" s="55"/>
     </x:row>
     <x:row r="73" ht="30" customHeight="1">
       <x:c r="A73" s="54"/>
@@ -1701,6 +1776,7 @@
       <x:c r="H73" s="55"/>
       <x:c r="I73" s="55"/>
       <x:c r="J73" s="57"/>
+      <x:c r="K73" s="55"/>
     </x:row>
     <x:row r="74" ht="30" customHeight="1">
       <x:c r="A74" s="54"/>
@@ -1713,6 +1789,7 @@
       <x:c r="H74" s="55"/>
       <x:c r="I74" s="55"/>
       <x:c r="J74" s="57"/>
+      <x:c r="K74" s="55"/>
     </x:row>
     <x:row r="75" ht="30" customHeight="1">
       <x:c r="A75" s="54"/>
@@ -1725,6 +1802,7 @@
       <x:c r="H75" s="55"/>
       <x:c r="I75" s="55"/>
       <x:c r="J75" s="57"/>
+      <x:c r="K75" s="55"/>
     </x:row>
     <x:row r="76" ht="30" customHeight="1">
       <x:c r="A76" s="54"/>
@@ -1737,6 +1815,7 @@
       <x:c r="H76" s="55"/>
       <x:c r="I76" s="55"/>
       <x:c r="J76" s="57"/>
+      <x:c r="K76" s="55"/>
     </x:row>
     <x:row r="77" ht="30" customHeight="1">
       <x:c r="A77" s="54"/>
@@ -1749,6 +1828,7 @@
       <x:c r="H77" s="55"/>
       <x:c r="I77" s="55"/>
       <x:c r="J77" s="57"/>
+      <x:c r="K77" s="55"/>
     </x:row>
     <x:row r="78" ht="30" customHeight="1">
       <x:c r="A78" s="54"/>
@@ -1761,6 +1841,7 @@
       <x:c r="H78" s="55"/>
       <x:c r="I78" s="55"/>
       <x:c r="J78" s="57"/>
+      <x:c r="K78" s="55"/>
     </x:row>
     <x:row r="79" ht="30" customHeight="1">
       <x:c r="A79" s="54"/>
@@ -1773,6 +1854,7 @@
       <x:c r="H79" s="55"/>
       <x:c r="I79" s="55"/>
       <x:c r="J79" s="57"/>
+      <x:c r="K79" s="55"/>
     </x:row>
     <x:row r="80" ht="30" customHeight="1">
       <x:c r="A80" s="54"/>
@@ -1785,6 +1867,7 @@
       <x:c r="H80" s="55"/>
       <x:c r="I80" s="55"/>
       <x:c r="J80" s="57"/>
+      <x:c r="K80" s="55"/>
     </x:row>
     <x:row r="81" ht="30" customHeight="1">
       <x:c r="A81" s="54"/>
@@ -1797,6 +1880,7 @@
       <x:c r="H81" s="55"/>
       <x:c r="I81" s="55"/>
       <x:c r="J81" s="57"/>
+      <x:c r="K81" s="55"/>
     </x:row>
     <x:row r="82" ht="30" customHeight="1">
       <x:c r="A82" s="54"/>
@@ -1809,6 +1893,7 @@
       <x:c r="H82" s="55"/>
       <x:c r="I82" s="55"/>
       <x:c r="J82" s="57"/>
+      <x:c r="K82" s="55"/>
     </x:row>
     <x:row r="83" ht="30" customHeight="1">
       <x:c r="A83" s="54"/>
@@ -1821,6 +1906,7 @@
       <x:c r="H83" s="55"/>
       <x:c r="I83" s="55"/>
       <x:c r="J83" s="57"/>
+      <x:c r="K83" s="55"/>
     </x:row>
     <x:row r="84" ht="30" customHeight="1">
       <x:c r="A84" s="54"/>
@@ -1833,6 +1919,7 @@
       <x:c r="H84" s="55"/>
       <x:c r="I84" s="55"/>
       <x:c r="J84" s="57"/>
+      <x:c r="K84" s="55"/>
     </x:row>
     <x:row r="85" ht="30" customHeight="1">
       <x:c r="A85" s="54"/>
@@ -1845,6 +1932,7 @@
       <x:c r="H85" s="55"/>
       <x:c r="I85" s="55"/>
       <x:c r="J85" s="57"/>
+      <x:c r="K85" s="55"/>
     </x:row>
     <x:row r="86" ht="30" customHeight="1">
       <x:c r="A86" s="54"/>
@@ -1857,6 +1945,7 @@
       <x:c r="H86" s="55"/>
       <x:c r="I86" s="55"/>
       <x:c r="J86" s="57"/>
+      <x:c r="K86" s="55"/>
     </x:row>
     <x:row r="87" ht="30" customHeight="1">
       <x:c r="A87" s="54"/>
@@ -1869,6 +1958,7 @@
       <x:c r="H87" s="55"/>
       <x:c r="I87" s="55"/>
       <x:c r="J87" s="57"/>
+      <x:c r="K87" s="55"/>
     </x:row>
     <x:row r="88" ht="30" customHeight="1">
       <x:c r="A88" s="54"/>
@@ -1881,6 +1971,7 @@
       <x:c r="H88" s="55"/>
       <x:c r="I88" s="55"/>
       <x:c r="J88" s="57"/>
+      <x:c r="K88" s="55"/>
     </x:row>
     <x:row r="89" ht="30" customHeight="1">
       <x:c r="A89" s="54"/>
@@ -1893,6 +1984,7 @@
       <x:c r="H89" s="55"/>
       <x:c r="I89" s="55"/>
       <x:c r="J89" s="57"/>
+      <x:c r="K89" s="55"/>
     </x:row>
     <x:row r="90" ht="30" customHeight="1">
       <x:c r="A90" s="54"/>
@@ -1905,6 +1997,7 @@
       <x:c r="H90" s="55"/>
       <x:c r="I90" s="55"/>
       <x:c r="J90" s="57"/>
+      <x:c r="K90" s="55"/>
     </x:row>
     <x:row r="91" ht="30" customHeight="1">
       <x:c r="A91" s="54"/>
@@ -1917,6 +2010,7 @@
       <x:c r="H91" s="55"/>
       <x:c r="I91" s="55"/>
       <x:c r="J91" s="57"/>
+      <x:c r="K91" s="55"/>
     </x:row>
     <x:row r="92" ht="30" customHeight="1">
       <x:c r="A92" s="54"/>
@@ -1929,6 +2023,7 @@
       <x:c r="H92" s="55"/>
       <x:c r="I92" s="55"/>
       <x:c r="J92" s="57"/>
+      <x:c r="K92" s="55"/>
     </x:row>
     <x:row r="93" ht="30" customHeight="1">
       <x:c r="A93" s="54"/>
@@ -1941,6 +2036,7 @@
       <x:c r="H93" s="55"/>
       <x:c r="I93" s="55"/>
       <x:c r="J93" s="57"/>
+      <x:c r="K93" s="55"/>
     </x:row>
     <x:row r="94" ht="30" customHeight="1">
       <x:c r="A94" s="54"/>
@@ -1953,6 +2049,7 @@
       <x:c r="H94" s="55"/>
       <x:c r="I94" s="55"/>
       <x:c r="J94" s="57"/>
+      <x:c r="K94" s="55"/>
     </x:row>
     <x:row r="95" ht="30" customHeight="1">
       <x:c r="A95" s="54"/>
@@ -1965,6 +2062,7 @@
       <x:c r="H95" s="55"/>
       <x:c r="I95" s="55"/>
       <x:c r="J95" s="57"/>
+      <x:c r="K95" s="55"/>
     </x:row>
     <x:row r="96" ht="30" customHeight="1">
       <x:c r="A96" s="54"/>
@@ -1977,6 +2075,7 @@
       <x:c r="H96" s="55"/>
       <x:c r="I96" s="55"/>
       <x:c r="J96" s="57"/>
+      <x:c r="K96" s="55"/>
     </x:row>
     <x:row r="97" ht="30" customHeight="1">
       <x:c r="A97" s="54"/>
@@ -1989,6 +2088,7 @@
       <x:c r="H97" s="55"/>
       <x:c r="I97" s="55"/>
       <x:c r="J97" s="57"/>
+      <x:c r="K97" s="55"/>
     </x:row>
     <x:row r="98" ht="30" customHeight="1">
       <x:c r="A98" s="54"/>
@@ -2001,6 +2101,7 @@
       <x:c r="H98" s="55"/>
       <x:c r="I98" s="55"/>
       <x:c r="J98" s="57"/>
+      <x:c r="K98" s="55"/>
     </x:row>
     <x:row r="99" ht="30" customHeight="1">
       <x:c r="A99" s="54"/>
@@ -2013,6 +2114,7 @@
       <x:c r="H99" s="55"/>
       <x:c r="I99" s="55"/>
       <x:c r="J99" s="57"/>
+      <x:c r="K99" s="55"/>
     </x:row>
     <x:row r="100" ht="30" customHeight="1">
       <x:c r="A100" s="54"/>
@@ -2025,6 +2127,7 @@
       <x:c r="H100" s="55"/>
       <x:c r="I100" s="55"/>
       <x:c r="J100" s="57"/>
+      <x:c r="K100" s="55"/>
     </x:row>
     <x:row r="101" ht="30" customHeight="1">
       <x:c r="A101" s="54"/>
@@ -2037,9 +2140,10 @@
       <x:c r="H101" s="55"/>
       <x:c r="I101" s="55"/>
       <x:c r="J101" s="57"/>
+      <x:c r="K101" s="55"/>
     </x:row>
   </x:sheetData>
-  <x:dataValidations count="3">
+  <x:dataValidations count="4">
     <x:dataValidation type="whole" operator="between" sqref="E2:E101">
       <x:formula1>4</x:formula1>
       <x:formula2>90</x:formula2>
@@ -2052,6 +2156,9 @@
       <x:formula1>10</x:formula1>
       <x:formula2>250</x:formula2>
     </x:dataValidation>
+    <x:dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="クラス" error="Aクラス か Bクラス を選んでください。クラスの名前を変えた大会は、その名前を書きます。" promptTitle="クラス" prompt="クラス分けのある大会だけ書きます。▼から選びます（3勝以上はAクラス、2勝以下はBクラス）。" sqref="K2:K101">
+      <x:formula1>"Aクラス,Bクラス"</x:formula1>
+    </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/uizin-eventos/public/templates/Tournament_OS_選手入力テンプレート.xlsx
+++ b/uizin-eventos/public/templates/Tournament_OS_選手入力テンプレート.xlsx
@@ -311,7 +311,7 @@
     <x:xf numFmtId="200" fontId="13" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="200" fontId="13" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="201" fontId="13" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
